--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13963,2647 +13833,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>首岸第3期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>288 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>243 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,126万
-$26,125/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,129万
-$25,897/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$934万
-$23,876/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$803万
-$23,630/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$875万
-$25,805/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$873万
-$25,746/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$864万
-$25,496/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$862万
-$25,488/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,846万
-$26,071/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,587万
-$26,015/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,121万
-$26,019/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,127万
-$25,849/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$977万
-$24,999/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,152万
-$26,413/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$798万
-$23,481/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$792万
-$23,359/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$792万
-$23,354/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$782万
-$23,080/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$778万
-$23,027/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,591万
-$25,826/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,841万
-$26,007/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,581万
-$25,915/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,116万
-$25,898/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,122万
-$25,722/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$917万
-$23,464/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,143万
-$26,218/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$794万
-$23,363/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$789万
-$23,263/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$788万
-$23,241/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$778万
-$22,965/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$774万
-$22,912/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M8" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,443万
-$23,428/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,668万
-$23,562/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,575万
-$25,816/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,111万
-$25,777/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,117万
-$25,624/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$911万
-$23,287/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,138万
-$26,110/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$791万
-$23,253/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$786万
-$23,174/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$784万
-$23,131/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$776万
-$22,887/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$770万
-$22,790/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,578万
-$25,625/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,661万
-$23,462/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,569万
-$25,728/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,030万
-$23,893/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,013万
-$23,240/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$952万
-$24,356/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,133万
-$25,979/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$804万
-$23,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$783万
-$23,099/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$781万
-$23,050/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$773万
-$22,812/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$809万
-$23,946/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,431万
-$23,223/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,651万
-$23,324/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,564万
-$25,639/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,004万
-$23,301/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,065万
-$24,434/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$897万
-$22,931/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,128万
-$25,862/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$799万
-$23,510/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$796万
-$23,488/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$778万
-$22,935/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$770万
-$22,704/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$764万
-$22,591/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,567万
-$25,435/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,642万
-$23,187/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,559万
-$25,551/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,023万
-$23,731/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,006万
-$23,082/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$911万
-$23,295/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,123万
-$25,764/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$777万
-$22,865/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$776万
-$22,884/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$774万
-$22,836/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$767万
-$22,613/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$759万
-$22,457/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,417万
-$23,008/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,632万
-$23,048/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,095万
-$25,411/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,001万
-$22,965/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$904万
-$23,114/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,018万
-$23,355/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$773万
-$22,747/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$771万
-$22,745/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$771万
-$22,739/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$779万
-$22,973/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$756万
-$22,362/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,414万
-$22,949/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,624万
-$22,931/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,443万
-$23,655/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,092万
-$25,325/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$1,048万
-$24,044/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$880万
-$22,501/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,015万
-$23,282/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$769万
-$22,629/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$808万
-$23,830/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$765万
-$22,576/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$757万
-$22,328/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$751万
-$22,209/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,406万
-$22,831/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,612万
-$22,774/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,404万
-$23,011/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$990万
-$22,963/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$988万
-$22,656/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$874万
-$22,347/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,110万
-$25,470/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$763万
-$22,456/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$802万
-$23,660/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$802万
-$23,652/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$793万
-$23,394/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$746万
-$22,058/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M15" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,394万
-$22,638/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,688万
-$23,848/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,471万
-$24,109/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,084万
-$25,148/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$980万
-$22,487/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$869万
-$22,231/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,006万
-$23,067/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$759万
-$22,338/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$796万
-$23,493/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$755万
-$22,264/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$748万
-$22,063/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$758万
-$22,425/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,413万
-$22,936/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,673万
-$23,631/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,386万
-$22,722/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$1,035万
-$24,004/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$973万
-$22,324/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$863万
-$22,080/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$998万
-$22,881/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$772万
-$22,692/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$751万
-$22,159/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$792万
-$23,365/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$760万
-$22,432/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$738万
-$21,835/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,372万
-$22,273/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,577万
-$22,281/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,379万
-$22,602/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$976万
-$22,653/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$987万
-$22,629/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$855万
-$21,875/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$987万
-$22,633/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$751万
-$22,078/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$746万
-$22,009/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$746万
-$22,012/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$758万
-$22,350/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$735万
-$21,746/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,387万
-$22,518/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,569万
-$22,166/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,404万
-$23,015/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$970万
-$22,497/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$960万
-$22,013/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$895万
-$22,897/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,000万
-$22,947/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$745万
-$21,912/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$741万
-$21,867/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$744万
-$21,945/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$737万
-$21,730/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$730万
-$21,611/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,417万
-$22,998/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,561万
-$22,049/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,367万
-$22,404/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$965万
-$22,381/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$955万
-$21,898/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$842万
-$21,533/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$971万
-$22,280/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$758万
-$22,295/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$738万
-$21,783/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$782万
-$23,063/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$750万
-$22,128/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$744万
-$22,004/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,407万
-$22,836/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,553万
-$21,935/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,361万
-$22,305/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$979万
-$22,719/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$952万
-$21,829/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$835万
-$21,365/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$1,017万
-$23,322/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$738万
-$21,719/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$736万
-$21,703/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$755万
-$22,262/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$731万
-$21,577/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$725万
-$21,455/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,324万
-$21,497/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,580万
-$22,323/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,355万
-$22,210/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$972万
-$22,549/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$969万
-$22,235/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$876万
-$22,397/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$978万
-$22,427/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$735万
-$21,623/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$750万
-$22,117/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$735万
-$21,681/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$728万
-$21,480/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$722万
-$21,358/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,315万
-$21,348/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,539万
-$21,731/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,349万
-$22,117/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$945万
-$21,931/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$944万
-$21,662/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$871万
-$22,279/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$948万
-$21,742/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$731万
-$21,505/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$732万
-$21,601/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$772万
-$22,771/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$725万
-$21,383/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$735万
-$21,731/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,307万
-$21,215/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,618万
-$22,846/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,477万
-$24,220/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$940万
-$21,802/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$990万
-$22,716/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$822万
-$21,028/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$938万
-$21,516/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$743万
-$21,860/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$768万
-$22,643/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$767万
-$22,632/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$736万
-$21,722/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$731万
-$21,632/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,328万
-$21,567/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,528万
-$21,575/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,468万
-$24,072/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$934万
-$21,665/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$933万
-$21,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$819万
-$20,944/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$931万
-$21,343/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$724万
-$21,291/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$764万
-$22,544/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$764万
-$22,524/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$733万
-$21,623/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$751万
-$22,208/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,293万
-$20,989/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,604万
-$22,649/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,399万
-$22,938/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$928万
-$21,542/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$928万
-$21,295/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$815万
-$20,837/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$923万
-$21,176/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$758万
-$22,300/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$720万
-$21,233/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$758万
-$22,363/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$712万
-$21,013/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$723万
-$21,404/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,284万
-$20,841/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,548万
-$21,865/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,347万
-$22,087/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$923万
-$21,411/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$922万
-$21,147/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$808万
-$20,672/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$916万
-$21,007/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$752万
-$22,125/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$713万
-$21,045/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$752万
-$22,182/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$747万
-$22,046/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$703万
-$20,812/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M27" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,275万
-$20,695/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 708呎 (3房)
-$1,541万
-$21,771/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 610呎 (3房)
-$1,309万
-$21,464/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 431呎 (2房)
-$917万
-$21,283/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
-$917万
-$21,022/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$802万
-$20,504/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-$958万
-$21,983/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 340呎 (2房)
-$707万
-$20,804/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 339呎 (2房)
-$708万
-$20,892/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$708万
-$20,876/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$718万
-$21,190/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>L | 338呎 (2房)
-$699万
-$20,666/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,267万
-$20,564/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 669呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 573呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 394呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (2房)
-$796万
-$20,357/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 302呎 (2房)
-$727万
-$24,085/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 301呎 (2房)
-$724万
-$24,056/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 301呎 (2房)
-$723万
-$24,032/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 301呎 (2房)
-$757万
-$25,142/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>L | 301呎 (2房)
-$714万
-$23,705/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="inlineStr">
-        <is>
-          <t>M | 616呎 (3房)
-$1,256万
-$20,383/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +147,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +222,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -13833,4 +14011,2647 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1126万
+$26,125/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1129万
+$25,897/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$934万
+$23,876/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$803万
+$23,630/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$875万
+$25,805/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$873万
+$25,746/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$864万
+$25,496/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$862万
+$25,488/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1846万
+$26,071/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1587万
+$26,015/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1121万
+$26,019/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1127万
+$25,849/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$977万
+$24,999/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1152万
+$26,413/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$798万
+$23,481/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$792万
+$23,359/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$792万
+$23,354/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$782万
+$23,080/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$778万
+$23,027/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1591万
+$25,826/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1841万
+$26,007/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1581万
+$25,915/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1116万
+$25,898/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1122万
+$25,722/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$917万
+$23,464/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1143万
+$26,218/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$794万
+$23,363/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$789万
+$23,263/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$788万
+$23,241/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$778万
+$22,965/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$774万
+$22,912/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M7" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1443万
+$23,428/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1668万
+$23,562/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1575万
+$25,816/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1111万
+$25,777/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1117万
+$25,624/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$911万
+$23,287/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1138万
+$26,110/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$791万
+$23,253/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$786万
+$23,174/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$784万
+$23,131/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$776万
+$22,887/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$770万
+$22,790/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1578万
+$25,625/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1661万
+$23,462/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1569万
+$25,728/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1030万
+$23,893/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1013万
+$23,240/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$952万
+$24,356/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1133万
+$25,979/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$804万
+$23,649/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$783万
+$23,099/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$781万
+$23,050/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$773万
+$22,812/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$809万
+$23,946/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1431万
+$23,223/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1651万
+$23,324/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1564万
+$25,639/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1004万
+$23,301/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1065万
+$24,434/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$897万
+$22,931/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1128万
+$25,862/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$799万
+$23,510/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$796万
+$23,488/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$778万
+$22,935/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$770万
+$22,704/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$764万
+$22,591/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1567万
+$25,435/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1642万
+$23,187/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1559万
+$25,551/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1023万
+$23,731/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1006万
+$23,082/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$911万
+$23,295/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1123万
+$25,764/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$777万
+$22,865/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$776万
+$22,884/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$774万
+$22,836/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$767万
+$22,613/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$759万
+$22,457/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1417万
+$23,008/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1632万
+$23,048/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1095万
+$25,411/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1001万
+$22,965/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$904万
+$23,114/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1018万
+$23,355/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$773万
+$22,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$771万
+$22,745/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$771万
+$22,739/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$779万
+$22,973/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$756万
+$22,362/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1414万
+$22,949/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1624万
+$22,931/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1443万
+$23,655/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1092万
+$25,325/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$1048万
+$24,044/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$880万
+$22,501/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1015万
+$23,282/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$769万
+$22,629/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$808万
+$23,830/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$765万
+$22,576/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$757万
+$22,328/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$751万
+$22,209/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1406万
+$22,831/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1612万
+$22,774/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1404万
+$23,011/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$990万
+$22,963/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$988万
+$22,656/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$874万
+$22,347/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1110万
+$25,470/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$763万
+$22,456/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$802万
+$23,660/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$802万
+$23,652/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$793万
+$23,394/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$746万
+$22,058/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1394万
+$22,638/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1688万
+$23,848/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1471万
+$24,109/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1084万
+$25,148/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$980万
+$22,487/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$869万
+$22,231/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1006万
+$23,067/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$759万
+$22,338/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$796万
+$23,493/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$755万
+$22,264/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$748万
+$22,063/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$758万
+$22,425/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1413万
+$22,936/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1673万
+$23,631/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1386万
+$22,722/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$1035万
+$24,004/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$973万
+$22,324/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$863万
+$22,080/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$998万
+$22,881/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$772万
+$22,692/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$751万
+$22,159/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$792万
+$23,365/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$760万
+$22,432/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$738万
+$21,835/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1372万
+$22,273/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1577万
+$22,281/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1379万
+$22,602/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$976万
+$22,653/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$987万
+$22,629/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$855万
+$21,875/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$987万
+$22,633/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$751万
+$22,078/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$746万
+$22,009/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$746万
+$22,012/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$758万
+$22,350/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$735万
+$21,746/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1387万
+$22,518/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1569万
+$22,166/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1404万
+$23,015/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$970万
+$22,497/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$960万
+$22,013/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$895万
+$22,897/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1000万
+$22,947/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$745万
+$21,912/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$741万
+$21,867/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$744万
+$21,945/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$737万
+$21,730/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$730万
+$21,611/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1417万
+$22,998/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1561万
+$22,049/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1367万
+$22,404/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$965万
+$22,381/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$955万
+$21,898/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$842万
+$21,533/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$971万
+$22,280/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$758万
+$22,295/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$738万
+$21,783/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$782万
+$23,063/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$750万
+$22,128/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$744万
+$22,004/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1407万
+$22,836/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1553万
+$21,935/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1361万
+$22,305/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$979万
+$22,719/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$952万
+$21,829/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$835万
+$21,365/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$1017万
+$23,322/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$738万
+$21,719/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$736万
+$21,703/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$755万
+$22,262/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$731万
+$21,577/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$725万
+$21,455/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1324万
+$21,497/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1580万
+$22,323/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1355万
+$22,210/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$972万
+$22,549/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$969万
+$22,235/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$876万
+$22,397/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$978万
+$22,427/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$735万
+$21,623/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$750万
+$22,117/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$735万
+$21,681/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$728万
+$21,480/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$722万
+$21,358/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1315万
+$21,348/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1539万
+$21,731/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1349万
+$22,117/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$945万
+$21,931/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$944万
+$21,662/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$871万
+$22,279/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$948万
+$21,742/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$731万
+$21,505/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$732万
+$21,601/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$772万
+$22,771/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$725万
+$21,383/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$735万
+$21,731/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1307万
+$21,215/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1618万
+$22,846/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1477万
+$24,220/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$940万
+$21,802/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$990万
+$22,716/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$822万
+$21,028/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$938万
+$21,516/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$743万
+$21,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$768万
+$22,643/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$767万
+$22,632/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$736万
+$21,722/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$731万
+$21,632/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1328万
+$21,567/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1528万
+$21,575/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1468万
+$24,072/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$934万
+$21,665/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$933万
+$21,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$819万
+$20,944/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$931万
+$21,343/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$724万
+$21,291/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$764万
+$22,544/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$764万
+$22,524/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$733万
+$21,623/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$751万
+$22,208/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1293万
+$20,989/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1604万
+$22,649/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1399万
+$22,938/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$928万
+$21,542/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$928万
+$21,295/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$815万
+$20,837/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$923万
+$21,176/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$758万
+$22,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$720万
+$21,233/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$758万
+$22,363/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$712万
+$21,013/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$723万
+$21,404/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1284万
+$20,841/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1548万
+$21,865/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1347万
+$22,087/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$923万
+$21,411/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$922万
+$21,147/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$808万
+$20,672/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$916万
+$21,007/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$752万
+$22,125/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$713万
+$21,045/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$752万
+$22,182/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$747万
+$22,046/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$703万
+$20,812/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1275万
+$20,695/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 708呎 (3房)
+$1541万
+$21,771/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 610呎 (3房)
+$1309万
+$21,464/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 431呎 (2房)
+$917万
+$21,283/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+$917万
+$21,022/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$802万
+$20,504/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+$958万
+$21,983/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 340呎 (2房)
+$707万
+$20,804/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 339呎 (2房)
+$708万
+$20,892/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$708万
+$20,876/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$718万
+$21,190/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>L | 338呎 (2房)
+$699万
+$20,666/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1267万
+$20,564/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 669呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 573呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 394呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (2房)
+$796万
+$20,357/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 302呎 (2房)
+$727万
+$24,085/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 301呎 (2房)
+$724万
+$24,056/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 301呎 (2房)
+$723万
+$24,032/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 301呎 (2房)
+$757万
+$25,142/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>L | 301呎 (2房)
+$714万
+$23,705/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>M | 616呎 (3房)
+$1256万
+$20,383/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -652,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J290"/>
+  <dimension ref="A1:N290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -712,6 +716,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -762,6 +786,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -808,6 +852,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7839650</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>23194</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -854,6 +914,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7865130</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>23201</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -900,6 +976,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>7942480</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>23429</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -946,6 +1038,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7960680</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>23483</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -992,6 +1100,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>8034300</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>23630</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1042,6 +1166,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1088,6 +1232,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9335600</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>23876</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1134,6 +1294,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10274810</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>23566</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1180,6 +1356,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>10246600</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>23774</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1230,6 +1422,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1280,6 +1492,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1326,6 +1558,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>14477190</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>23502</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1372,6 +1620,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7783200</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>23027</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1418,6 +1682,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7824100</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>23080</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1464,6 +1744,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7917000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>23354</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1510,6 +1806,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7918800</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>23359</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1556,6 +1868,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7983400</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>23481</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1602,6 +1930,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>10479560</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>24036</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1648,6 +1992,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>9774700</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>24999</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1694,6 +2054,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>10255700</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>23522</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1740,6 +2116,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>10204740</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>23677</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1786,6 +2178,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>14440790</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>23673</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1832,6 +2240,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>16796780</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>23724</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1878,6 +2302,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>14431600</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>23428</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1924,6 +2364,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7744100</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>22912</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1970,6 +2426,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7785000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>22965</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2016,6 +2488,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>7878700</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>23241</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2062,6 +2550,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>7886000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>23263</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2108,6 +2612,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7943300</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>23363</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2154,6 +2674,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>10402210</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>23858</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2200,6 +2736,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>9174600</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>23464</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2246,6 +2798,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>10205650</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>23407</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2292,6 +2860,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>10157420</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>23567</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2338,6 +2922,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>14385280</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>23582</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2384,6 +2984,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>16755830</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>23666</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2430,6 +3046,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>14364350</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>23319</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2476,6 +3108,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7703100</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22790</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2522,6 +3170,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>7758600</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22887</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2568,6 +3232,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>7841400</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>23131</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2614,6 +3294,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>7856000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>23174</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2660,6 +3356,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>7906000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>23253</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2706,6 +3418,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>10359440</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>23760</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2752,6 +3480,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>9105400</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>23287</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2798,6 +3542,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>10166520</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>23318</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2844,6 +3604,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>10110100</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>23457</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2890,6 +3666,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>14330680</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>23493</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2936,6 +3728,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>16682100</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>23562</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2982,6 +3790,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>14305200</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>23223</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3028,6 +3852,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>8093700</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>23946</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3074,6 +3914,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>7733100</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22812</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3120,6 +3976,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>7814100</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>23050</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3166,6 +4038,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>7830500</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>23099</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3212,6 +4100,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>8040700</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>23649</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3258,6 +4162,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>10307570</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>23641</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3304,6 +4224,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>9523200</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>24356</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3350,6 +4286,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>10132800</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>23240</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3396,6 +4348,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>10297800</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>23893</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3442,6 +4410,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>14281540</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>23412</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3488,6 +4472,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>16611100</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23462</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3534,6 +4534,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>14257880</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>23146</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3580,6 +4596,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>7635800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>22591</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3626,6 +4658,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>7696700</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22704</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3672,6 +4720,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>7775000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22935</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3718,6 +4782,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>7962600</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>23488</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3764,6 +4844,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7993300</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>23510</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3810,6 +4906,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>10261160</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23535</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3856,6 +4968,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>8966200</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>22931</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3902,6 +5030,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>10653100</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>24434</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3948,6 +5092,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>10042700</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>23301</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3994,6 +5154,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>14232400</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>23332</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4040,6 +5216,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>16513700</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>23324</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4086,6 +5278,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>14173200</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>23008</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4132,6 +5340,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>7590300</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>22457</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4178,6 +5402,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>7665800</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>22613</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4224,6 +5464,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>7741300</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>22836</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4270,6 +5526,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>7757700</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>22884</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4316,6 +5588,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>7774100</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>22865</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4362,6 +5650,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>10222030</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>23445</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4408,6 +5712,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>9108400</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>23295</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4454,6 +5774,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>10063600</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>23082</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4500,6 +5836,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>10228100</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>23731</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4546,6 +5898,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>14183260</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>23251</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4592,6 +5960,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>16416400</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>23187</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4638,6 +6022,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>14136800</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>22949</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4684,6 +6084,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>7558400</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>22362</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4730,6 +6146,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7787800</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>22973</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4776,6 +6208,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7708600</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>22739</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4822,6 +6270,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7710400</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>22745</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4868,6 +6332,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>7734000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>22747</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4914,6 +6394,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>10182900</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>23355</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4960,6 +6456,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>9037700</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>23114</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5006,6 +6518,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>10012700</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>22965</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5052,6 +6580,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>9966320</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>23124</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5102,6 +6646,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5148,6 +6712,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>16318100</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>23048</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5194,6 +6774,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>14064000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>22831</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5240,6 +6836,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>7506500</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>22209</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5286,6 +6898,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7569300</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>22328</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5332,6 +6960,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>7653100</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>22576</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5378,6 +7022,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>8078400</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>23830</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5424,6 +7084,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>7694000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>22629</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5470,6 +7146,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>10151000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>23282</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5516,6 +7208,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>8797800</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>22501</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5562,6 +7270,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>10483200</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>24044</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5608,6 +7332,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>9932650</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>23046</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5654,6 +7394,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>14429800</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>23655</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5700,6 +7456,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>16235300</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>22931</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5746,6 +7518,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>13944800</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>22638</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5792,6 +7580,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7455600</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>22058</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5838,6 +7642,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7930500</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>23394</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5884,6 +7704,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>8017900</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>23652</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5930,6 +7766,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>8020800</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>23660</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5976,6 +7828,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>7634900</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>22456</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6022,6 +7890,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>10105550</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>23178</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6068,6 +7952,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>8737800</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>22347</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6114,6 +8014,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>9878000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>22656</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6160,6 +8076,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>9897100</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>22963</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6206,6 +8138,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>14036700</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>23011</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6252,6 +8200,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>16124200</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>22774</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6298,6 +8262,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>14128500</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>22936</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6344,6 +8324,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>7579500</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>22425</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6390,6 +8386,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>7479200</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22063</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6436,6 +8448,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>7547500</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>22264</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6482,6 +8510,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>7964100</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>23493</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6528,6 +8572,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7594800</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>22338</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6574,6 +8634,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>10057300</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23067</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6620,6 +8696,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>8692300</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>22231</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6666,6 +8758,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>9804300</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>22487</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6712,6 +8820,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>9863490</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>22885</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6758,6 +8882,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>14706200</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>24109</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6804,6 +8944,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>16884400</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>23848</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6850,6 +9006,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>13720000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>22273</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6896,6 +9068,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>7380100</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>21835</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6942,6 +9130,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>7604600</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>22432</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6988,6 +9192,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7920900</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>23365</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7034,6 +9254,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>7512000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>22159</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7080,6 +9316,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>7715200</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>22692</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7126,6 +9378,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>9976300</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22881</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7172,6 +9440,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>8633100</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>22080</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7218,6 +9502,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>9733300</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>22324</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7264,6 +9564,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>10345900</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>24004</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7310,6 +9626,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>13860200</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>22722</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7356,6 +9688,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>16730800</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>23631</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7402,6 +9750,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>13870900</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>22518</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7448,6 +9812,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>21746</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7494,6 +9874,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>7576700</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>22350</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7540,6 +9936,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>7462000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7586,6 +9998,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>7461000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>22009</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7632,6 +10060,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>7506500</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>22078</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7678,6 +10122,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>9868000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>22633</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7724,6 +10184,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>8553000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21875</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7770,6 +10246,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>9866300</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>22629</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7816,6 +10308,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>9763300</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>22653</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7862,6 +10370,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>13787400</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>22602</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7908,6 +10432,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>15774800</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>22281</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7954,6 +10494,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>14166700</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>22998</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8000,6 +10556,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>7304500</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>21611</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8046,6 +10618,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>7366400</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>21730</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8092,6 +10680,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>7439200</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21945</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8138,6 +10742,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>7412800</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>21867</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8184,6 +10804,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>7450100</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>21912</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8230,6 +10866,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>10004900</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>22947</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8276,6 +10928,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>8952900</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>22897</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8322,6 +10990,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>9597700</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>22013</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8368,6 +11052,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>9696000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>22497</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8414,6 +11114,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>14039200</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>23015</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8460,6 +11176,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>15693800</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>22166</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8506,6 +11238,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>14066800</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>22836</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8552,6 +11300,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>7437200</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>22004</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8598,6 +11362,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>7501300</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>22128</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8644,6 +11424,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>7818200</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>23063</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8690,6 +11486,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>7384600</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>21783</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8736,6 +11548,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>7580400</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>22295</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8782,6 +11610,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>9714200</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>22280</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8828,6 +11672,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>8419300</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>21533</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8874,6 +11734,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>9547700</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>21898</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8920,6 +11796,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>9646000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>22381</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8966,6 +11858,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>13666300</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>22404</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9012,6 +11920,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>15611000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>22049</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9058,6 +11982,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>13242300</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>21497</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9104,6 +12044,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>7251700</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>21455</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9150,6 +12106,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>7314500</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>21577</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9196,6 +12168,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>7546900</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>22262</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9242,6 +12230,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>7357300</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>21703</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9288,6 +12292,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>7384600</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>21719</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9334,6 +12354,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>10168300</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>23322</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9380,6 +12416,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>8353800</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>21365</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9426,6 +12478,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>9517600</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>21829</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9472,6 +12540,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>9791900</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>22719</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9518,6 +12602,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>13606300</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>22305</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9564,6 +12664,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>15530000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>21935</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9610,6 +12726,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>13150400</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>21348</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9656,6 +12788,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>7219000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>21358</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9702,6 +12850,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7281800</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>21480</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9748,6 +12912,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>21681</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9794,6 +12974,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>7497600</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>22117</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9840,6 +13036,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>7351800</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>21623</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9886,6 +13098,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>9778000</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>22427</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9932,6 +13160,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>8757100</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>22397</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9978,6 +13222,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>9694300</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>22235</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10024,6 +13284,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>9718500</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>22549</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10070,6 +13346,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>13548000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>22210</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10116,6 +13408,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>15804400</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>22323</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10162,6 +13470,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>13068500</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>21215</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10208,6 +13532,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>7345100</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>21731</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10254,6 +13594,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7249000</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>21383</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10300,6 +13656,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>7719300</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>22771</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10346,6 +13718,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>7322700</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>21601</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10392,6 +13780,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>7311800</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>21505</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10438,6 +13842,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>9479400</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>21742</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10484,6 +13904,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>8711000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>22279</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10530,6 +13966,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>9444800</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>21662</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10576,6 +14028,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>9452100</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>21931</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10622,6 +14090,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>13491600</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>22117</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10668,6 +14152,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>15385300</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>21731</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10714,6 +14214,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>13285000</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>21567</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10760,6 +14276,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>7311600</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>21632</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10806,6 +14338,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7363700</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>21722</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10852,6 +14400,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>7672300</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>22632</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10898,6 +14462,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>7676100</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>22643</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10944,6 +14524,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>7432500</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>21860</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10990,6 +14586,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>9381100</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>21516</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11036,6 +14648,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>8221800</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>21028</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11082,6 +14710,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>9904300</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>22716</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11128,6 +14772,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>9396600</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>21802</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11174,6 +14834,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>13444340</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>22040</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11220,6 +14896,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>16175000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>22846</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11266,6 +14958,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>12929200</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>20989</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11312,6 +15020,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>7506200</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>22208</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11358,6 +15082,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7330200</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>21623</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11404,6 +15144,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>7635800</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>22524</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11450,6 +15206,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>7642500</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>22544</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11496,6 +15268,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>7239000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>21291</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11542,6 +15330,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>9305600</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>21343</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11588,6 +15392,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>8189000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>20944</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11634,6 +15454,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>9330200</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>21400</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11680,6 +15516,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>9337500</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>21665</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11726,6 +15578,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>13362440</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>21906</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11772,6 +15640,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>15275200</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>21575</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11818,6 +15702,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>12838200</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>20841</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11864,6 +15764,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>7234400</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>21404</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11910,6 +15826,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>7123400</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>21013</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11956,6 +15888,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>7581100</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>22363</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12002,6 +15950,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>7198100</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>21233</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12048,6 +16012,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7582000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>22300</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12094,6 +16074,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>9232800</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>21176</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12140,6 +16136,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>8147200</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>20837</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12186,6 +16198,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>9284700</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>21295</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12232,6 +16260,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>9284700</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>21542</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12278,6 +16322,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>13992000</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>22938</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12324,6 +16384,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>16035800</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>22649</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12370,6 +16446,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>12748100</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>20695</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12416,6 +16508,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>7034300</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>20812</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12462,6 +16570,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>7473600</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>22046</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12508,6 +16632,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>7519600</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>22182</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12554,6 +16694,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>7134400</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>21045</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12600,6 +16756,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>7522500</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>22125</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12646,6 +16818,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>9159100</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>21007</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12692,6 +16880,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>8082600</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>20672</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12738,6 +16942,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>9220100</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>21147</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12784,6 +17004,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>9228300</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>21411</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12830,6 +17066,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>13472900</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>22087</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12876,6 +17128,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>15480700</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>21865</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12922,6 +17190,22 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>12667200</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>20564</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12968,6 +17252,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>6985100</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>20666</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13014,6 +17314,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>7183300</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>21190</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13060,6 +17376,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>7077000</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>20876</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13106,6 +17438,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>7082500</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>20892</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13152,6 +17500,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>7073400</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>20804</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13198,6 +17562,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>9584600</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>21983</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13244,6 +17624,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>8017100</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>20504</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13290,6 +17686,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>9165500</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>21022</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13336,6 +17748,22 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>9172800</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>21283</v>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13382,6 +17810,22 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>13093000</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>21464</v>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13428,6 +17872,22 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>15413800</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>21771</v>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13474,6 +17934,22 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>12556100</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>20383</v>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13520,6 +17996,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>7135300</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>23705</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13566,6 +18058,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>7567600</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>25142</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13612,6 +18120,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>7233500</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>24032</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13658,6 +18182,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>7240800</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>24056</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13704,6 +18244,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>7273600</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>24085</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13754,6 +18310,26 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13800,6 +18376,22 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>7959700</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>20357</v>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13850,6 +18442,26 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13900,6 +18512,26 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13950,6 +18582,26 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14000,13 +18652,33 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -14218,7 +18890,7 @@
           <t>E | 391呎 (2房)
 $934万
 $23,876/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -14234,7 +18906,7 @@
           <t>G | 340呎 (2房)
 $803万
 $23,630/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -14321,7 +18993,7 @@
           <t>E | 391呎 (2房)
 $977万
 $24,999/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -14337,7 +19009,7 @@
           <t>G | 340呎 (2房)
 $798万
 $23,481/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -14345,7 +19017,7 @@
           <t>H | 339呎 (2房)
 $792万
 $23,359/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -14353,7 +19025,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,354/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -14361,7 +19033,7 @@
           <t>K | 339呎 (2房)
 $782万
 $23,080/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -14369,7 +19041,7 @@
           <t>L | 338呎 (2房)
 $778万
 $23,027/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -14424,7 +19096,7 @@
           <t>E | 391呎 (2房)
 $917万
 $23,464/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -14440,7 +19112,7 @@
           <t>G | 340呎 (2房)
 $794万
 $23,363/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -14448,7 +19120,7 @@
           <t>H | 339呎 (2房)
 $789万
 $23,263/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -14456,7 +19128,7 @@
           <t>J | 339呎 (2房)
 $788万
 $23,241/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -14464,7 +19136,7 @@
           <t>K | 339呎 (2房)
 $778万
 $22,965/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -14472,7 +19144,7 @@
           <t>L | 338呎 (2房)
 $774万
 $22,912/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -14480,7 +19152,7 @@
           <t>M | 616呎 (3房)
 $1443万
 $23,428/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -14495,7 +19167,7 @@
           <t>A | 708呎 (3房)
 $1668万
 $23,562/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -14527,7 +19199,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,287/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -14543,7 +19215,7 @@
           <t>G | 340呎 (2房)
 $791万
 $23,253/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -14551,7 +19223,7 @@
           <t>H | 339呎 (2房)
 $786万
 $23,174/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -14559,7 +19231,7 @@
           <t>J | 339呎 (2房)
 $784万
 $23,131/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -14567,7 +19239,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,887/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -14575,7 +19247,7 @@
           <t>L | 338呎 (2房)
 $770万
 $22,790/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -14598,7 +19270,7 @@
           <t>A | 708呎 (3房)
 $1661万
 $23,462/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -14614,7 +19286,7 @@
           <t>C | 431呎 (2房)
 $1030万
 $23,893/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -14622,7 +19294,7 @@
           <t>D | 436呎 (2房)
 $1013万
 $23,240/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -14630,7 +19302,7 @@
           <t>E | 391呎 (2房)
 $952万
 $24,356/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -14646,7 +19318,7 @@
           <t>G | 340呎 (2房)
 $804万
 $23,649/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -14654,7 +19326,7 @@
           <t>H | 339呎 (2房)
 $783万
 $23,099/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -14662,7 +19334,7 @@
           <t>J | 339呎 (2房)
 $781万
 $23,050/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -14670,7 +19342,7 @@
           <t>K | 339呎 (2房)
 $773万
 $22,812/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -14678,7 +19350,7 @@
           <t>L | 338呎 (2房)
 $809万
 $23,946/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -14686,7 +19358,7 @@
           <t>M | 616呎 (3房)
 $1431万
 $23,223/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -14701,7 +19373,7 @@
           <t>A | 708呎 (3房)
 $1651万
 $23,324/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -14717,7 +19389,7 @@
           <t>C | 431呎 (2房)
 $1004万
 $23,301/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -14725,7 +19397,7 @@
           <t>D | 436呎 (2房)
 $1065万
 $24,434/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -14733,7 +19405,7 @@
           <t>E | 391呎 (2房)
 $897万
 $22,931/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -14749,7 +19421,7 @@
           <t>G | 340呎 (2房)
 $799万
 $23,510/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -14757,7 +19429,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,488/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -14765,7 +19437,7 @@
           <t>J | 339呎 (2房)
 $778万
 $22,935/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -14773,7 +19445,7 @@
           <t>K | 339呎 (2房)
 $770万
 $22,704/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -14781,7 +19453,7 @@
           <t>L | 338呎 (2房)
 $764万
 $22,591/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -14804,7 +19476,7 @@
           <t>A | 708呎 (3房)
 $1642万
 $23,187/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -14820,7 +19492,7 @@
           <t>C | 431呎 (2房)
 $1023万
 $23,731/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -14828,7 +19500,7 @@
           <t>D | 436呎 (2房)
 $1006万
 $23,082/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -14836,7 +19508,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,295/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -14852,7 +19524,7 @@
           <t>G | 340呎 (2房)
 $777万
 $22,865/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -14860,7 +19532,7 @@
           <t>H | 339呎 (2房)
 $776万
 $22,884/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -14868,7 +19540,7 @@
           <t>J | 339呎 (2房)
 $774万
 $22,836/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -14876,7 +19548,7 @@
           <t>K | 339呎 (2房)
 $767万
 $22,613/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -14884,7 +19556,7 @@
           <t>L | 338呎 (2房)
 $759万
 $22,457/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -14892,7 +19564,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $23,008/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -14907,7 +19579,7 @@
           <t>A | 708呎 (3房)
 $1632万
 $23,048/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14931,7 +19603,7 @@
           <t>D | 436呎 (2房)
 $1001万
 $22,965/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -14939,7 +19611,7 @@
           <t>E | 391呎 (2房)
 $904万
 $23,114/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -14947,7 +19619,7 @@
           <t>F | 436呎 (2房)
 $1018万
 $23,355/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -14955,7 +19627,7 @@
           <t>G | 340呎 (2房)
 $773万
 $22,747/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -14963,7 +19635,7 @@
           <t>H | 339呎 (2房)
 $771万
 $22,745/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -14971,7 +19643,7 @@
           <t>J | 339呎 (2房)
 $771万
 $22,739/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -14979,7 +19651,7 @@
           <t>K | 339呎 (2房)
 $779万
 $22,973/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -14987,7 +19659,7 @@
           <t>L | 338呎 (2房)
 $756万
 $22,362/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -14995,7 +19667,7 @@
           <t>M | 616呎 (3房)
 $1414万
 $22,949/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -15010,7 +19682,7 @@
           <t>A | 708呎 (3房)
 $1624万
 $22,931/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -15018,7 +19690,7 @@
           <t>B | 610呎 (3房)
 $1443万
 $23,655/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -15034,7 +19706,7 @@
           <t>D | 436呎 (2房)
 $1048万
 $24,044/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -15042,7 +19714,7 @@
           <t>E | 391呎 (2房)
 $880万
 $22,501/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -15050,7 +19722,7 @@
           <t>F | 436呎 (2房)
 $1015万
 $23,282/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -15058,7 +19730,7 @@
           <t>G | 340呎 (2房)
 $769万
 $22,629/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -15066,7 +19738,7 @@
           <t>H | 339呎 (2房)
 $808万
 $23,830/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -15074,7 +19746,7 @@
           <t>J | 339呎 (2房)
 $765万
 $22,576/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -15082,7 +19754,7 @@
           <t>K | 339呎 (2房)
 $757万
 $22,328/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -15090,7 +19762,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,209/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -15098,7 +19770,7 @@
           <t>M | 616呎 (3房)
 $1406万
 $22,831/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -15113,7 +19785,7 @@
           <t>A | 708呎 (3房)
 $1612万
 $22,774/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -15121,7 +19793,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,011/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -15129,7 +19801,7 @@
           <t>C | 431呎 (2房)
 $990万
 $22,963/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -15137,7 +19809,7 @@
           <t>D | 436呎 (2房)
 $988万
 $22,656/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -15145,7 +19817,7 @@
           <t>E | 391呎 (2房)
 $874万
 $22,347/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -15161,7 +19833,7 @@
           <t>G | 340呎 (2房)
 $763万
 $22,456/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -15169,7 +19841,7 @@
           <t>H | 339呎 (2房)
 $802万
 $23,660/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -15177,7 +19849,7 @@
           <t>J | 339呎 (2房)
 $802万
 $23,652/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -15185,7 +19857,7 @@
           <t>K | 339呎 (2房)
 $793万
 $23,394/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -15193,7 +19865,7 @@
           <t>L | 338呎 (2房)
 $746万
 $22,058/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -15201,7 +19873,7 @@
           <t>M | 616呎 (3房)
 $1394万
 $22,638/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -15216,7 +19888,7 @@
           <t>A | 708呎 (3房)
 $1688万
 $23,848/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -15224,7 +19896,7 @@
           <t>B | 610呎 (3房)
 $1471万
 $24,109/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -15240,7 +19912,7 @@
           <t>D | 436呎 (2房)
 $980万
 $22,487/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -15248,7 +19920,7 @@
           <t>E | 391呎 (2房)
 $869万
 $22,231/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -15256,7 +19928,7 @@
           <t>F | 436呎 (2房)
 $1006万
 $23,067/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -15264,7 +19936,7 @@
           <t>G | 340呎 (2房)
 $759万
 $22,338/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -15272,7 +19944,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,493/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -15280,7 +19952,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,264/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -15288,7 +19960,7 @@
           <t>K | 339呎 (2房)
 $748万
 $22,063/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -15296,7 +19968,7 @@
           <t>L | 338呎 (2房)
 $758万
 $22,425/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -15304,7 +19976,7 @@
           <t>M | 616呎 (3房)
 $1413万
 $22,936/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -15319,7 +19991,7 @@
           <t>A | 708呎 (3房)
 $1673万
 $23,631/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -15327,7 +19999,7 @@
           <t>B | 610呎 (3房)
 $1386万
 $22,722/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -15335,7 +20007,7 @@
           <t>C | 431呎 (2房)
 $1035万
 $24,004/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -15343,7 +20015,7 @@
           <t>D | 436呎 (2房)
 $973万
 $22,324/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -15351,7 +20023,7 @@
           <t>E | 391呎 (2房)
 $863万
 $22,080/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -15359,7 +20031,7 @@
           <t>F | 436呎 (2房)
 $998万
 $22,881/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -15367,7 +20039,7 @@
           <t>G | 340呎 (2房)
 $772万
 $22,692/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -15375,7 +20047,7 @@
           <t>H | 339呎 (2房)
 $751万
 $22,159/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -15383,7 +20055,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,365/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -15391,7 +20063,7 @@
           <t>K | 339呎 (2房)
 $760万
 $22,432/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -15399,7 +20071,7 @@
           <t>L | 338呎 (2房)
 $738万
 $21,835/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -15407,7 +20079,7 @@
           <t>M | 616呎 (3房)
 $1372万
 $22,273/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -15422,7 +20094,7 @@
           <t>A | 708呎 (3房)
 $1577万
 $22,281/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -15430,7 +20102,7 @@
           <t>B | 610呎 (3房)
 $1379万
 $22,602/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -15438,7 +20110,7 @@
           <t>C | 431呎 (2房)
 $976万
 $22,653/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -15446,7 +20118,7 @@
           <t>D | 436呎 (2房)
 $987万
 $22,629/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -15454,7 +20126,7 @@
           <t>E | 391呎 (2房)
 $855万
 $21,875/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -15462,7 +20134,7 @@
           <t>F | 436呎 (2房)
 $987万
 $22,633/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -15470,7 +20142,7 @@
           <t>G | 340呎 (2房)
 $751万
 $22,078/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -15478,7 +20150,7 @@
           <t>H | 339呎 (2房)
 $746万
 $22,009/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -15486,7 +20158,7 @@
           <t>J | 339呎 (2房)
 $746万
 $22,012/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -15494,7 +20166,7 @@
           <t>K | 339呎 (2房)
 $758万
 $22,350/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -15502,7 +20174,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,746/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -15510,7 +20182,7 @@
           <t>M | 616呎 (3房)
 $1387万
 $22,518/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -15525,7 +20197,7 @@
           <t>A | 708呎 (3房)
 $1569万
 $22,166/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -15533,7 +20205,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,015/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -15541,7 +20213,7 @@
           <t>C | 431呎 (2房)
 $970万
 $22,497/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -15549,7 +20221,7 @@
           <t>D | 436呎 (2房)
 $960万
 $22,013/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -15557,7 +20229,7 @@
           <t>E | 391呎 (2房)
 $895万
 $22,897/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -15565,7 +20237,7 @@
           <t>F | 436呎 (2房)
 $1000万
 $22,947/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -15573,7 +20245,7 @@
           <t>G | 340呎 (2房)
 $745万
 $21,912/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -15581,7 +20253,7 @@
           <t>H | 339呎 (2房)
 $741万
 $21,867/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -15589,7 +20261,7 @@
           <t>J | 339呎 (2房)
 $744万
 $21,945/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -15597,7 +20269,7 @@
           <t>K | 339呎 (2房)
 $737万
 $21,730/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -15605,7 +20277,7 @@
           <t>L | 338呎 (2房)
 $730万
 $21,611/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -15613,7 +20285,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $22,998/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -15628,7 +20300,7 @@
           <t>A | 708呎 (3房)
 $1561万
 $22,049/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -15636,7 +20308,7 @@
           <t>B | 610呎 (3房)
 $1367万
 $22,404/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -15644,7 +20316,7 @@
           <t>C | 431呎 (2房)
 $965万
 $22,381/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -15652,7 +20324,7 @@
           <t>D | 436呎 (2房)
 $955万
 $21,898/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -15660,7 +20332,7 @@
           <t>E | 391呎 (2房)
 $842万
 $21,533/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -15668,7 +20340,7 @@
           <t>F | 436呎 (2房)
 $971万
 $22,280/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -15676,7 +20348,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,295/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -15684,7 +20356,7 @@
           <t>H | 339呎 (2房)
 $738万
 $21,783/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -15692,7 +20364,7 @@
           <t>J | 339呎 (2房)
 $782万
 $23,063/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -15700,7 +20372,7 @@
           <t>K | 339呎 (2房)
 $750万
 $22,128/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -15708,7 +20380,7 @@
           <t>L | 338呎 (2房)
 $744万
 $22,004/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -15716,7 +20388,7 @@
           <t>M | 616呎 (3房)
 $1407万
 $22,836/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -15731,7 +20403,7 @@
           <t>A | 708呎 (3房)
 $1553万
 $21,935/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -15739,7 +20411,7 @@
           <t>B | 610呎 (3房)
 $1361万
 $22,305/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -15747,7 +20419,7 @@
           <t>C | 431呎 (2房)
 $979万
 $22,719/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -15755,7 +20427,7 @@
           <t>D | 436呎 (2房)
 $952万
 $21,829/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -15763,7 +20435,7 @@
           <t>E | 391呎 (2房)
 $835万
 $21,365/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -15771,7 +20443,7 @@
           <t>F | 436呎 (2房)
 $1017万
 $23,322/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -15779,7 +20451,7 @@
           <t>G | 340呎 (2房)
 $738万
 $21,719/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -15787,7 +20459,7 @@
           <t>H | 339呎 (2房)
 $736万
 $21,703/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -15795,7 +20467,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,262/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -15803,7 +20475,7 @@
           <t>K | 339呎 (2房)
 $731万
 $21,577/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -15811,7 +20483,7 @@
           <t>L | 338呎 (2房)
 $725万
 $21,455/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -15819,7 +20491,7 @@
           <t>M | 616呎 (3房)
 $1324万
 $21,497/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -15834,7 +20506,7 @@
           <t>A | 708呎 (3房)
 $1580万
 $22,323/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -15842,7 +20514,7 @@
           <t>B | 610呎 (3房)
 $1355万
 $22,210/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -15850,7 +20522,7 @@
           <t>C | 431呎 (2房)
 $972万
 $22,549/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -15858,7 +20530,7 @@
           <t>D | 436呎 (2房)
 $969万
 $22,235/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -15866,7 +20538,7 @@
           <t>E | 391呎 (2房)
 $876万
 $22,397/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -15874,7 +20546,7 @@
           <t>F | 436呎 (2房)
 $978万
 $22,427/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -15882,7 +20554,7 @@
           <t>G | 340呎 (2房)
 $735万
 $21,623/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -15890,7 +20562,7 @@
           <t>H | 339呎 (2房)
 $750万
 $22,117/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -15898,7 +20570,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -15906,7 +20578,7 @@
           <t>K | 339呎 (2房)
 $728万
 $21,480/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -15914,7 +20586,7 @@
           <t>L | 338呎 (2房)
 $722万
 $21,358/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -15922,7 +20594,7 @@
           <t>M | 616呎 (3房)
 $1315万
 $21,348/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -15937,7 +20609,7 @@
           <t>A | 708呎 (3房)
 $1539万
 $21,731/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -15945,7 +20617,7 @@
           <t>B | 610呎 (3房)
 $1349万
 $22,117/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -15953,7 +20625,7 @@
           <t>C | 431呎 (2房)
 $945万
 $21,931/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -15961,7 +20633,7 @@
           <t>D | 436呎 (2房)
 $944万
 $21,662/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -15969,7 +20641,7 @@
           <t>E | 391呎 (2房)
 $871万
 $22,279/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -15977,7 +20649,7 @@
           <t>F | 436呎 (2房)
 $948万
 $21,742/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -15985,7 +20657,7 @@
           <t>G | 340呎 (2房)
 $731万
 $21,505/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -15993,7 +20665,7 @@
           <t>H | 339呎 (2房)
 $732万
 $21,601/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -16001,7 +20673,7 @@
           <t>J | 339呎 (2房)
 $772万
 $22,771/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -16009,7 +20681,7 @@
           <t>K | 339呎 (2房)
 $725万
 $21,383/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -16017,7 +20689,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,731/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -16025,7 +20697,7 @@
           <t>M | 616呎 (3房)
 $1307万
 $21,215/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -16040,7 +20712,7 @@
           <t>A | 708呎 (3房)
 $1618万
 $22,846/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -16056,7 +20728,7 @@
           <t>C | 431呎 (2房)
 $940万
 $21,802/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -16064,7 +20736,7 @@
           <t>D | 436呎 (2房)
 $990万
 $22,716/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -16072,7 +20744,7 @@
           <t>E | 391呎 (2房)
 $822万
 $21,028/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -16080,7 +20752,7 @@
           <t>F | 436呎 (2房)
 $938万
 $21,516/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -16088,7 +20760,7 @@
           <t>G | 340呎 (2房)
 $743万
 $21,860/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -16096,7 +20768,7 @@
           <t>H | 339呎 (2房)
 $768万
 $22,643/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -16104,7 +20776,7 @@
           <t>J | 339呎 (2房)
 $767万
 $22,632/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -16112,7 +20784,7 @@
           <t>K | 339呎 (2房)
 $736万
 $21,722/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -16120,7 +20792,7 @@
           <t>L | 338呎 (2房)
 $731万
 $21,632/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -16128,7 +20800,7 @@
           <t>M | 616呎 (3房)
 $1328万
 $21,567/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -16143,7 +20815,7 @@
           <t>A | 708呎 (3房)
 $1528万
 $21,575/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -16159,7 +20831,7 @@
           <t>C | 431呎 (2房)
 $934万
 $21,665/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -16167,7 +20839,7 @@
           <t>D | 436呎 (2房)
 $933万
 $21,400/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -16175,7 +20847,7 @@
           <t>E | 391呎 (2房)
 $819万
 $20,944/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -16183,7 +20855,7 @@
           <t>F | 436呎 (2房)
 $931万
 $21,343/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -16191,7 +20863,7 @@
           <t>G | 340呎 (2房)
 $724万
 $21,291/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -16199,7 +20871,7 @@
           <t>H | 339呎 (2房)
 $764万
 $22,544/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -16207,7 +20879,7 @@
           <t>J | 339呎 (2房)
 $764万
 $22,524/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -16215,7 +20887,7 @@
           <t>K | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -16223,7 +20895,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,208/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -16231,7 +20903,7 @@
           <t>M | 616呎 (3房)
 $1293万
 $20,989/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -16246,7 +20918,7 @@
           <t>A | 708呎 (3房)
 $1604万
 $22,649/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -16254,7 +20926,7 @@
           <t>B | 610呎 (3房)
 $1399万
 $22,938/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -16262,7 +20934,7 @@
           <t>C | 431呎 (2房)
 $928万
 $21,542/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -16270,7 +20942,7 @@
           <t>D | 436呎 (2房)
 $928万
 $21,295/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -16278,7 +20950,7 @@
           <t>E | 391呎 (2房)
 $815万
 $20,837/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -16286,7 +20958,7 @@
           <t>F | 436呎 (2房)
 $923万
 $21,176/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -16294,7 +20966,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,300/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -16302,7 +20974,7 @@
           <t>H | 339呎 (2房)
 $720万
 $21,233/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -16310,7 +20982,7 @@
           <t>J | 339呎 (2房)
 $758万
 $22,363/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -16318,7 +20990,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,013/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -16326,7 +20998,7 @@
           <t>L | 338呎 (2房)
 $723万
 $21,404/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -16334,7 +21006,7 @@
           <t>M | 616呎 (3房)
 $1284万
 $20,841/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -16349,7 +21021,7 @@
           <t>A | 708呎 (3房)
 $1548万
 $21,865/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -16357,7 +21029,7 @@
           <t>B | 610呎 (3房)
 $1347万
 $22,087/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -16365,7 +21037,7 @@
           <t>C | 431呎 (2房)
 $923万
 $21,411/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -16373,7 +21045,7 @@
           <t>D | 436呎 (2房)
 $922万
 $21,147/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -16381,7 +21053,7 @@
           <t>E | 391呎 (2房)
 $808万
 $20,672/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -16389,7 +21061,7 @@
           <t>F | 436呎 (2房)
 $916万
 $21,007/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -16397,7 +21069,7 @@
           <t>G | 340呎 (2房)
 $752万
 $22,125/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -16405,7 +21077,7 @@
           <t>H | 339呎 (2房)
 $713万
 $21,045/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -16413,7 +21085,7 @@
           <t>J | 339呎 (2房)
 $752万
 $22,182/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -16421,7 +21093,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,046/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -16429,7 +21101,7 @@
           <t>L | 338呎 (2房)
 $703万
 $20,812/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -16437,7 +21109,7 @@
           <t>M | 616呎 (3房)
 $1275万
 $20,695/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -16452,7 +21124,7 @@
           <t>A | 708呎 (3房)
 $1541万
 $21,771/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -16460,7 +21132,7 @@
           <t>B | 610呎 (3房)
 $1309万
 $21,464/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -16468,7 +21140,7 @@
           <t>C | 431呎 (2房)
 $917万
 $21,283/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -16476,7 +21148,7 @@
           <t>D | 436呎 (2房)
 $917万
 $21,022/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -16484,7 +21156,7 @@
           <t>E | 391呎 (2房)
 $802万
 $20,504/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -16492,7 +21164,7 @@
           <t>F | 436呎 (2房)
 $958万
 $21,983/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -16500,7 +21172,7 @@
           <t>G | 340呎 (2房)
 $707万
 $20,804/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -16508,7 +21180,7 @@
           <t>H | 339呎 (2房)
 $708万
 $20,892/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -16516,7 +21188,7 @@
           <t>J | 339呎 (2房)
 $708万
 $20,876/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -16524,7 +21196,7 @@
           <t>K | 339呎 (2房)
 $718万
 $21,190/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -16532,7 +21204,7 @@
           <t>L | 338呎 (2房)
 $699万
 $20,666/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -16540,7 +21212,7 @@
           <t>M | 616呎 (3房)
 $1267万
 $20,564/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -16587,7 +21259,7 @@
           <t>E | 391呎 (2房)
 $796万
 $20,357/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -16603,7 +21275,7 @@
           <t>G | 302呎 (2房)
 $727万
 $24,085/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -16611,7 +21283,7 @@
           <t>H | 301呎 (2房)
 $724万
 $24,056/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -16619,7 +21291,7 @@
           <t>J | 301呎 (2房)
 $723万
 $24,032/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -16627,7 +21299,7 @@
           <t>K | 301呎 (2房)
 $757万
 $25,142/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -16635,7 +21307,7 @@
           <t>L | 301呎 (2房)
 $714万
 $23,705/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -16643,7 +21315,7 @@
           <t>M | 616呎 (3房)
 $1256万
 $20,383/呎
-(26年-05月)</t>
+(26年-05月-09日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -657,7 +657,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2240,18 +2240,18 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>16796780</v>
+        <v>16796700</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>23724</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -14834,18 +14834,18 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K229" s="5" t="n">
-        <v>13444340</v>
+        <v>13444300</v>
       </c>
       <c r="L229" s="5" t="n">
         <v>22040</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -18890,7 +18890,7 @@
           <t>E | 391呎 (2房)
 $934万
 $23,876/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -18906,7 +18906,7 @@
           <t>G | 340呎 (2房)
 $803万
 $23,630/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>E | 391呎 (2房)
 $977万
 $24,999/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -19009,7 +19009,7 @@
           <t>G | 340呎 (2房)
 $798万
 $23,481/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -19017,7 +19017,7 @@
           <t>H | 339呎 (2房)
 $792万
 $23,359/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -19025,7 +19025,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,354/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -19033,7 +19033,7 @@
           <t>K | 339呎 (2房)
 $782万
 $23,080/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -19041,7 +19041,7 @@
           <t>L | 338呎 (2房)
 $778万
 $23,027/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -19096,7 +19096,7 @@
           <t>E | 391呎 (2房)
 $917万
 $23,464/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -19112,7 +19112,7 @@
           <t>G | 340呎 (2房)
 $794万
 $23,363/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -19120,7 +19120,7 @@
           <t>H | 339呎 (2房)
 $789万
 $23,263/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -19128,7 +19128,7 @@
           <t>J | 339呎 (2房)
 $788万
 $23,241/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -19136,7 +19136,7 @@
           <t>K | 339呎 (2房)
 $778万
 $22,965/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>L | 338呎 (2房)
 $774万
 $22,912/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -19152,7 +19152,7 @@
           <t>M | 616呎 (3房)
 $1443万
 $23,428/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -19167,7 +19167,7 @@
           <t>A | 708呎 (3房)
 $1668万
 $23,562/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19199,7 +19199,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,287/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -19215,7 +19215,7 @@
           <t>G | 340呎 (2房)
 $791万
 $23,253/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -19223,7 +19223,7 @@
           <t>H | 339呎 (2房)
 $786万
 $23,174/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -19231,7 +19231,7 @@
           <t>J | 339呎 (2房)
 $784万
 $23,131/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -19239,7 +19239,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,887/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -19247,7 +19247,7 @@
           <t>L | 338呎 (2房)
 $770万
 $22,790/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -19270,7 +19270,7 @@
           <t>A | 708呎 (3房)
 $1661万
 $23,462/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19286,7 +19286,7 @@
           <t>C | 431呎 (2房)
 $1030万
 $23,893/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19294,7 +19294,7 @@
           <t>D | 436呎 (2房)
 $1013万
 $23,240/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -19302,7 +19302,7 @@
           <t>E | 391呎 (2房)
 $952万
 $24,356/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -19318,7 +19318,7 @@
           <t>G | 340呎 (2房)
 $804万
 $23,649/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -19326,7 +19326,7 @@
           <t>H | 339呎 (2房)
 $783万
 $23,099/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -19334,7 +19334,7 @@
           <t>J | 339呎 (2房)
 $781万
 $23,050/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -19342,7 +19342,7 @@
           <t>K | 339呎 (2房)
 $773万
 $22,812/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -19350,7 +19350,7 @@
           <t>L | 338呎 (2房)
 $809万
 $23,946/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -19358,7 +19358,7 @@
           <t>M | 616呎 (3房)
 $1431万
 $23,223/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
           <t>A | 708呎 (3房)
 $1651万
 $23,324/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -19389,7 +19389,7 @@
           <t>C | 431呎 (2房)
 $1004万
 $23,301/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19397,7 +19397,7 @@
           <t>D | 436呎 (2房)
 $1065万
 $24,434/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -19405,7 +19405,7 @@
           <t>E | 391呎 (2房)
 $897万
 $22,931/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -19421,7 +19421,7 @@
           <t>G | 340呎 (2房)
 $799万
 $23,510/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -19429,7 +19429,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,488/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -19437,7 +19437,7 @@
           <t>J | 339呎 (2房)
 $778万
 $22,935/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -19445,7 +19445,7 @@
           <t>K | 339呎 (2房)
 $770万
 $22,704/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>L | 338呎 (2房)
 $764万
 $22,591/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -19476,7 +19476,7 @@
           <t>A | 708呎 (3房)
 $1642万
 $23,187/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>C | 431呎 (2房)
 $1023万
 $23,731/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>D | 436呎 (2房)
 $1006万
 $23,082/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,295/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -19524,7 +19524,7 @@
           <t>G | 340呎 (2房)
 $777万
 $22,865/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -19532,7 +19532,7 @@
           <t>H | 339呎 (2房)
 $776万
 $22,884/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -19540,7 +19540,7 @@
           <t>J | 339呎 (2房)
 $774万
 $22,836/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -19548,7 +19548,7 @@
           <t>K | 339呎 (2房)
 $767万
 $22,613/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -19556,7 +19556,7 @@
           <t>L | 338呎 (2房)
 $759万
 $22,457/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -19564,7 +19564,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $23,008/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
           <t>A | 708呎 (3房)
 $1632万
 $23,048/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19603,7 +19603,7 @@
           <t>D | 436呎 (2房)
 $1001万
 $22,965/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -19611,7 +19611,7 @@
           <t>E | 391呎 (2房)
 $904万
 $23,114/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19619,7 +19619,7 @@
           <t>F | 436呎 (2房)
 $1018万
 $23,355/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>G | 340呎 (2房)
 $773万
 $22,747/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>H | 339呎 (2房)
 $771万
 $22,745/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>J | 339呎 (2房)
 $771万
 $22,739/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -19651,7 +19651,7 @@
           <t>K | 339呎 (2房)
 $779万
 $22,973/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>L | 338呎 (2房)
 $756万
 $22,362/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -19667,7 +19667,7 @@
           <t>M | 616呎 (3房)
 $1414万
 $22,949/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19682,7 @@
           <t>A | 708呎 (3房)
 $1624万
 $22,931/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19690,7 +19690,7 @@
           <t>B | 610呎 (3房)
 $1443万
 $23,655/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -19706,7 +19706,7 @@
           <t>D | 436呎 (2房)
 $1048万
 $24,044/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -19714,7 +19714,7 @@
           <t>E | 391呎 (2房)
 $880万
 $22,501/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -19722,7 +19722,7 @@
           <t>F | 436呎 (2房)
 $1015万
 $23,282/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -19730,7 +19730,7 @@
           <t>G | 340呎 (2房)
 $769万
 $22,629/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -19738,7 +19738,7 @@
           <t>H | 339呎 (2房)
 $808万
 $23,830/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
           <t>J | 339呎 (2房)
 $765万
 $22,576/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -19754,7 +19754,7 @@
           <t>K | 339呎 (2房)
 $757万
 $22,328/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -19762,7 +19762,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,209/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -19770,7 +19770,7 @@
           <t>M | 616呎 (3房)
 $1406万
 $22,831/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
           <t>A | 708呎 (3房)
 $1612万
 $22,774/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19793,7 +19793,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,011/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19801,7 +19801,7 @@
           <t>C | 431呎 (2房)
 $990万
 $22,963/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19809,7 +19809,7 @@
           <t>D | 436呎 (2房)
 $988万
 $22,656/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -19817,7 +19817,7 @@
           <t>E | 391呎 (2房)
 $874万
 $22,347/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -19833,7 +19833,7 @@
           <t>G | 340呎 (2房)
 $763万
 $22,456/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -19841,7 +19841,7 @@
           <t>H | 339呎 (2房)
 $802万
 $23,660/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -19849,7 +19849,7 @@
           <t>J | 339呎 (2房)
 $802万
 $23,652/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -19857,7 +19857,7 @@
           <t>K | 339呎 (2房)
 $793万
 $23,394/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -19865,7 +19865,7 @@
           <t>L | 338呎 (2房)
 $746万
 $22,058/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -19873,7 +19873,7 @@
           <t>M | 616呎 (3房)
 $1394万
 $22,638/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
           <t>A | 708呎 (3房)
 $1688万
 $23,848/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19896,7 +19896,7 @@
           <t>B | 610呎 (3房)
 $1471万
 $24,109/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -19912,7 +19912,7 @@
           <t>D | 436呎 (2房)
 $980万
 $22,487/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -19920,7 +19920,7 @@
           <t>E | 391呎 (2房)
 $869万
 $22,231/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19928,7 +19928,7 @@
           <t>F | 436呎 (2房)
 $1006万
 $23,067/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -19936,7 +19936,7 @@
           <t>G | 340呎 (2房)
 $759万
 $22,338/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,493/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,264/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>K | 339呎 (2房)
 $748万
 $22,063/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>L | 338呎 (2房)
 $758万
 $22,425/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>M | 616呎 (3房)
 $1413万
 $22,936/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
           <t>A | 708呎 (3房)
 $1673万
 $23,631/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19999,7 +19999,7 @@
           <t>B | 610呎 (3房)
 $1386万
 $22,722/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20007,7 +20007,7 @@
           <t>C | 431呎 (2房)
 $1035万
 $24,004/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20015,7 +20015,7 @@
           <t>D | 436呎 (2房)
 $973万
 $22,324/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -20023,7 +20023,7 @@
           <t>E | 391呎 (2房)
 $863万
 $22,080/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>F | 436呎 (2房)
 $998万
 $22,881/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>G | 340呎 (2房)
 $772万
 $22,692/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>H | 339呎 (2房)
 $751万
 $22,159/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,365/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>K | 339呎 (2房)
 $760万
 $22,432/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>L | 338呎 (2房)
 $738万
 $21,835/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>M | 616呎 (3房)
 $1372万
 $22,273/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
           <t>A | 708呎 (3房)
 $1577万
 $22,281/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>B | 610呎 (3房)
 $1379万
 $22,602/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>C | 431呎 (2房)
 $976万
 $22,653/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>D | 436呎 (2房)
 $987万
 $22,629/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>E | 391呎 (2房)
 $855万
 $21,875/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>F | 436呎 (2房)
 $987万
 $22,633/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>G | 340呎 (2房)
 $751万
 $22,078/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>H | 339呎 (2房)
 $746万
 $22,009/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>J | 339呎 (2房)
 $746万
 $22,012/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>K | 339呎 (2房)
 $758万
 $22,350/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,746/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>M | 616呎 (3房)
 $1387万
 $22,518/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -20197,7 +20197,7 @@
           <t>A | 708呎 (3房)
 $1569万
 $22,166/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,015/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>C | 431呎 (2房)
 $970万
 $22,497/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>D | 436呎 (2房)
 $960万
 $22,013/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>E | 391呎 (2房)
 $895万
 $22,897/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>F | 436呎 (2房)
 $1000万
 $22,947/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>G | 340呎 (2房)
 $745万
 $21,912/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -20253,7 +20253,7 @@
           <t>H | 339呎 (2房)
 $741万
 $21,867/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -20261,7 +20261,7 @@
           <t>J | 339呎 (2房)
 $744万
 $21,945/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -20269,7 +20269,7 @@
           <t>K | 339呎 (2房)
 $737万
 $21,730/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -20277,7 +20277,7 @@
           <t>L | 338呎 (2房)
 $730万
 $21,611/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -20285,7 +20285,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $22,998/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20300,7 @@
           <t>A | 708呎 (3房)
 $1561万
 $22,049/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>B | 610呎 (3房)
 $1367万
 $22,404/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>C | 431呎 (2房)
 $965万
 $22,381/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>D | 436呎 (2房)
 $955万
 $21,898/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -20332,7 +20332,7 @@
           <t>E | 391呎 (2房)
 $842万
 $21,533/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -20340,7 +20340,7 @@
           <t>F | 436呎 (2房)
 $971万
 $22,280/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -20348,7 +20348,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,295/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -20356,7 +20356,7 @@
           <t>H | 339呎 (2房)
 $738万
 $21,783/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>J | 339呎 (2房)
 $782万
 $23,063/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>K | 339呎 (2房)
 $750万
 $22,128/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>L | 338呎 (2房)
 $744万
 $22,004/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>M | 616呎 (3房)
 $1407万
 $22,836/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
           <t>A | 708呎 (3房)
 $1553万
 $21,935/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20411,7 +20411,7 @@
           <t>B | 610呎 (3房)
 $1361万
 $22,305/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20419,7 +20419,7 @@
           <t>C | 431呎 (2房)
 $979万
 $22,719/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20427,7 +20427,7 @@
           <t>D | 436呎 (2房)
 $952万
 $21,829/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -20435,7 +20435,7 @@
           <t>E | 391呎 (2房)
 $835万
 $21,365/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -20443,7 +20443,7 @@
           <t>F | 436呎 (2房)
 $1017万
 $23,322/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -20451,7 +20451,7 @@
           <t>G | 340呎 (2房)
 $738万
 $21,719/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -20459,7 +20459,7 @@
           <t>H | 339呎 (2房)
 $736万
 $21,703/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -20467,7 +20467,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,262/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -20475,7 +20475,7 @@
           <t>K | 339呎 (2房)
 $731万
 $21,577/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -20483,7 +20483,7 @@
           <t>L | 338呎 (2房)
 $725万
 $21,455/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -20491,7 +20491,7 @@
           <t>M | 616呎 (3房)
 $1324万
 $21,497/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20506,7 @@
           <t>A | 708呎 (3房)
 $1580万
 $22,323/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 610呎 (3房)
 $1355万
 $22,210/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 431呎 (2房)
 $972万
 $22,549/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20530,7 +20530,7 @@
           <t>D | 436呎 (2房)
 $969万
 $22,235/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 391呎 (2房)
 $876万
 $22,397/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -20546,7 +20546,7 @@
           <t>F | 436呎 (2房)
 $978万
 $22,427/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -20554,7 +20554,7 @@
           <t>G | 340呎 (2房)
 $735万
 $21,623/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -20562,7 +20562,7 @@
           <t>H | 339呎 (2房)
 $750万
 $22,117/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -20570,7 +20570,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -20578,7 +20578,7 @@
           <t>K | 339呎 (2房)
 $728万
 $21,480/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -20586,7 +20586,7 @@
           <t>L | 338呎 (2房)
 $722万
 $21,358/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>M | 616呎 (3房)
 $1315万
 $21,348/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
           <t>A | 708呎 (3房)
 $1539万
 $21,731/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20617,7 +20617,7 @@
           <t>B | 610呎 (3房)
 $1349万
 $22,117/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20625,7 +20625,7 @@
           <t>C | 431呎 (2房)
 $945万
 $21,931/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>D | 436呎 (2房)
 $944万
 $21,662/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>E | 391呎 (2房)
 $871万
 $22,279/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>F | 436呎 (2房)
 $948万
 $21,742/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -20657,7 +20657,7 @@
           <t>G | 340呎 (2房)
 $731万
 $21,505/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -20665,7 +20665,7 @@
           <t>H | 339呎 (2房)
 $732万
 $21,601/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -20673,7 +20673,7 @@
           <t>J | 339呎 (2房)
 $772万
 $22,771/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -20681,7 +20681,7 @@
           <t>K | 339呎 (2房)
 $725万
 $21,383/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -20689,7 +20689,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,731/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -20697,7 +20697,7 @@
           <t>M | 616呎 (3房)
 $1307万
 $21,215/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
           <t>A | 708呎 (3房)
 $1618万
 $22,846/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -20728,7 +20728,7 @@
           <t>C | 431呎 (2房)
 $940万
 $21,802/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -20736,7 +20736,7 @@
           <t>D | 436呎 (2房)
 $990万
 $22,716/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -20744,7 +20744,7 @@
           <t>E | 391呎 (2房)
 $822万
 $21,028/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -20752,7 +20752,7 @@
           <t>F | 436呎 (2房)
 $938万
 $21,516/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -20760,7 +20760,7 @@
           <t>G | 340呎 (2房)
 $743万
 $21,860/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -20768,7 +20768,7 @@
           <t>H | 339呎 (2房)
 $768万
 $22,643/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -20776,7 +20776,7 @@
           <t>J | 339呎 (2房)
 $767万
 $22,632/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -20784,7 +20784,7 @@
           <t>K | 339呎 (2房)
 $736万
 $21,722/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -20792,7 +20792,7 @@
           <t>L | 338呎 (2房)
 $731万
 $21,632/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -20800,7 +20800,7 @@
           <t>M | 616呎 (3房)
 $1328万
 $21,567/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -20815,7 +20815,7 @@
           <t>A | 708呎 (3房)
 $1528万
 $21,575/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -20831,7 +20831,7 @@
           <t>C | 431呎 (2房)
 $934万
 $21,665/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -20839,7 +20839,7 @@
           <t>D | 436呎 (2房)
 $933万
 $21,400/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -20847,7 +20847,7 @@
           <t>E | 391呎 (2房)
 $819万
 $20,944/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -20855,7 +20855,7 @@
           <t>F | 436呎 (2房)
 $931万
 $21,343/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -20863,7 +20863,7 @@
           <t>G | 340呎 (2房)
 $724万
 $21,291/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -20871,7 +20871,7 @@
           <t>H | 339呎 (2房)
 $764万
 $22,544/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -20879,7 +20879,7 @@
           <t>J | 339呎 (2房)
 $764万
 $22,524/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -20887,7 +20887,7 @@
           <t>K | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -20895,7 +20895,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,208/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -20903,7 +20903,7 @@
           <t>M | 616呎 (3房)
 $1293万
 $20,989/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20918,7 @@
           <t>A | 708呎 (3房)
 $1604万
 $22,649/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -20926,7 +20926,7 @@
           <t>B | 610呎 (3房)
 $1399万
 $22,938/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -20934,7 +20934,7 @@
           <t>C | 431呎 (2房)
 $928万
 $21,542/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -20942,7 +20942,7 @@
           <t>D | 436呎 (2房)
 $928万
 $21,295/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -20950,7 +20950,7 @@
           <t>E | 391呎 (2房)
 $815万
 $20,837/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -20958,7 +20958,7 @@
           <t>F | 436呎 (2房)
 $923万
 $21,176/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -20966,7 +20966,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,300/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -20974,7 +20974,7 @@
           <t>H | 339呎 (2房)
 $720万
 $21,233/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -20982,7 +20982,7 @@
           <t>J | 339呎 (2房)
 $758万
 $22,363/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -20990,7 +20990,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,013/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -20998,7 +20998,7 @@
           <t>L | 338呎 (2房)
 $723万
 $21,404/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -21006,7 +21006,7 @@
           <t>M | 616呎 (3房)
 $1284万
 $20,841/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21021,7 @@
           <t>A | 708呎 (3房)
 $1548万
 $21,865/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21029,7 +21029,7 @@
           <t>B | 610呎 (3房)
 $1347万
 $22,087/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -21037,7 +21037,7 @@
           <t>C | 431呎 (2房)
 $923万
 $21,411/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -21045,7 +21045,7 @@
           <t>D | 436呎 (2房)
 $922万
 $21,147/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -21053,7 +21053,7 @@
           <t>E | 391呎 (2房)
 $808万
 $20,672/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -21061,7 +21061,7 @@
           <t>F | 436呎 (2房)
 $916万
 $21,007/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -21069,7 +21069,7 @@
           <t>G | 340呎 (2房)
 $752万
 $22,125/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -21077,7 +21077,7 @@
           <t>H | 339呎 (2房)
 $713万
 $21,045/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -21085,7 +21085,7 @@
           <t>J | 339呎 (2房)
 $752万
 $22,182/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -21093,7 +21093,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,046/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -21101,7 +21101,7 @@
           <t>L | 338呎 (2房)
 $703万
 $20,812/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -21109,7 +21109,7 @@
           <t>M | 616呎 (3房)
 $1275万
 $20,695/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21124,7 @@
           <t>A | 708呎 (3房)
 $1541万
 $21,771/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21132,7 +21132,7 @@
           <t>B | 610呎 (3房)
 $1309万
 $21,464/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -21140,7 +21140,7 @@
           <t>C | 431呎 (2房)
 $917万
 $21,283/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21148,7 +21148,7 @@
           <t>D | 436呎 (2房)
 $917万
 $21,022/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -21156,7 +21156,7 @@
           <t>E | 391呎 (2房)
 $802万
 $20,504/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -21164,7 +21164,7 @@
           <t>F | 436呎 (2房)
 $958万
 $21,983/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -21172,7 +21172,7 @@
           <t>G | 340呎 (2房)
 $707万
 $20,804/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -21180,7 +21180,7 @@
           <t>H | 339呎 (2房)
 $708万
 $20,892/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -21188,7 +21188,7 @@
           <t>J | 339呎 (2房)
 $708万
 $20,876/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -21196,7 +21196,7 @@
           <t>K | 339呎 (2房)
 $718万
 $21,190/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -21204,7 +21204,7 @@
           <t>L | 338呎 (2房)
 $699万
 $20,666/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -21212,7 +21212,7 @@
           <t>M | 616呎 (3房)
 $1267万
 $20,564/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
           <t>E | 391呎 (2房)
 $796万
 $20,357/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -21275,7 +21275,7 @@
           <t>G | 302呎 (2房)
 $727万
 $24,085/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -21283,7 +21283,7 @@
           <t>H | 301呎 (2房)
 $724万
 $24,056/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -21291,7 +21291,7 @@
           <t>J | 301呎 (2房)
 $723万
 $24,032/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -21299,7 +21299,7 @@
           <t>K | 301呎 (2房)
 $757万
 $25,142/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -21307,7 +21307,7 @@
           <t>L | 301呎 (2房)
 $714万
 $23,705/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -21315,7 +21315,7 @@
           <t>M | 616呎 (3房)
 $1256万
 $20,383/呎
-(26年-05月-09日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -18890,7 +18890,7 @@
           <t>E | 391呎 (2房)
 $934万
 $23,876/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -18906,7 +18906,7 @@
           <t>G | 340呎 (2房)
 $803万
 $23,630/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>E | 391呎 (2房)
 $977万
 $24,999/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -19009,7 +19009,7 @@
           <t>G | 340呎 (2房)
 $798万
 $23,481/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -19017,7 +19017,7 @@
           <t>H | 339呎 (2房)
 $792万
 $23,359/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -19025,7 +19025,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,354/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -19033,7 +19033,7 @@
           <t>K | 339呎 (2房)
 $782万
 $23,080/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -19041,7 +19041,7 @@
           <t>L | 338呎 (2房)
 $778万
 $23,027/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -19096,7 +19096,7 @@
           <t>E | 391呎 (2房)
 $917万
 $23,464/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -19112,7 +19112,7 @@
           <t>G | 340呎 (2房)
 $794万
 $23,363/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -19120,7 +19120,7 @@
           <t>H | 339呎 (2房)
 $789万
 $23,263/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -19128,7 +19128,7 @@
           <t>J | 339呎 (2房)
 $788万
 $23,241/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -19136,7 +19136,7 @@
           <t>K | 339呎 (2房)
 $778万
 $22,965/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>L | 338呎 (2房)
 $774万
 $22,912/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -19152,7 +19152,7 @@
           <t>M | 616呎 (3房)
 $1443万
 $23,428/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -19167,7 +19167,7 @@
           <t>A | 708呎 (3房)
 $1668万
 $23,562/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19199,7 +19199,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,287/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -19215,7 +19215,7 @@
           <t>G | 340呎 (2房)
 $791万
 $23,253/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -19223,7 +19223,7 @@
           <t>H | 339呎 (2房)
 $786万
 $23,174/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -19231,7 +19231,7 @@
           <t>J | 339呎 (2房)
 $784万
 $23,131/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -19239,7 +19239,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,887/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -19247,7 +19247,7 @@
           <t>L | 338呎 (2房)
 $770万
 $22,790/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -19270,7 +19270,7 @@
           <t>A | 708呎 (3房)
 $1661万
 $23,462/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19286,7 +19286,7 @@
           <t>C | 431呎 (2房)
 $1030万
 $23,893/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19294,7 +19294,7 @@
           <t>D | 436呎 (2房)
 $1013万
 $23,240/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -19302,7 +19302,7 @@
           <t>E | 391呎 (2房)
 $952万
 $24,356/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -19318,7 +19318,7 @@
           <t>G | 340呎 (2房)
 $804万
 $23,649/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -19326,7 +19326,7 @@
           <t>H | 339呎 (2房)
 $783万
 $23,099/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -19334,7 +19334,7 @@
           <t>J | 339呎 (2房)
 $781万
 $23,050/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -19342,7 +19342,7 @@
           <t>K | 339呎 (2房)
 $773万
 $22,812/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -19350,7 +19350,7 @@
           <t>L | 338呎 (2房)
 $809万
 $23,946/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -19358,7 +19358,7 @@
           <t>M | 616呎 (3房)
 $1431万
 $23,223/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
           <t>A | 708呎 (3房)
 $1651万
 $23,324/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -19389,7 +19389,7 @@
           <t>C | 431呎 (2房)
 $1004万
 $23,301/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19397,7 +19397,7 @@
           <t>D | 436呎 (2房)
 $1065万
 $24,434/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -19405,7 +19405,7 @@
           <t>E | 391呎 (2房)
 $897万
 $22,931/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -19421,7 +19421,7 @@
           <t>G | 340呎 (2房)
 $799万
 $23,510/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -19429,7 +19429,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,488/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -19437,7 +19437,7 @@
           <t>J | 339呎 (2房)
 $778万
 $22,935/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -19445,7 +19445,7 @@
           <t>K | 339呎 (2房)
 $770万
 $22,704/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>L | 338呎 (2房)
 $764万
 $22,591/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -19476,7 +19476,7 @@
           <t>A | 708呎 (3房)
 $1642万
 $23,187/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>C | 431呎 (2房)
 $1023万
 $23,731/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>D | 436呎 (2房)
 $1006万
 $23,082/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,295/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -19524,7 +19524,7 @@
           <t>G | 340呎 (2房)
 $777万
 $22,865/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -19532,7 +19532,7 @@
           <t>H | 339呎 (2房)
 $776万
 $22,884/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -19540,7 +19540,7 @@
           <t>J | 339呎 (2房)
 $774万
 $22,836/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -19548,7 +19548,7 @@
           <t>K | 339呎 (2房)
 $767万
 $22,613/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -19556,7 +19556,7 @@
           <t>L | 338呎 (2房)
 $759万
 $22,457/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -19564,7 +19564,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $23,008/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
           <t>A | 708呎 (3房)
 $1632万
 $23,048/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19603,7 +19603,7 @@
           <t>D | 436呎 (2房)
 $1001万
 $22,965/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -19611,7 +19611,7 @@
           <t>E | 391呎 (2房)
 $904万
 $23,114/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19619,7 +19619,7 @@
           <t>F | 436呎 (2房)
 $1018万
 $23,355/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>G | 340呎 (2房)
 $773万
 $22,747/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>H | 339呎 (2房)
 $771万
 $22,745/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>J | 339呎 (2房)
 $771万
 $22,739/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -19651,7 +19651,7 @@
           <t>K | 339呎 (2房)
 $779万
 $22,973/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>L | 338呎 (2房)
 $756万
 $22,362/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -19667,7 +19667,7 @@
           <t>M | 616呎 (3房)
 $1414万
 $22,949/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19682,7 @@
           <t>A | 708呎 (3房)
 $1624万
 $22,931/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19690,7 +19690,7 @@
           <t>B | 610呎 (3房)
 $1443万
 $23,655/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -19706,7 +19706,7 @@
           <t>D | 436呎 (2房)
 $1048万
 $24,044/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -19714,7 +19714,7 @@
           <t>E | 391呎 (2房)
 $880万
 $22,501/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -19722,7 +19722,7 @@
           <t>F | 436呎 (2房)
 $1015万
 $23,282/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -19730,7 +19730,7 @@
           <t>G | 340呎 (2房)
 $769万
 $22,629/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -19738,7 +19738,7 @@
           <t>H | 339呎 (2房)
 $808万
 $23,830/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
           <t>J | 339呎 (2房)
 $765万
 $22,576/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -19754,7 +19754,7 @@
           <t>K | 339呎 (2房)
 $757万
 $22,328/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -19762,7 +19762,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,209/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -19770,7 +19770,7 @@
           <t>M | 616呎 (3房)
 $1406万
 $22,831/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
           <t>A | 708呎 (3房)
 $1612万
 $22,774/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19793,7 +19793,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,011/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19801,7 +19801,7 @@
           <t>C | 431呎 (2房)
 $990万
 $22,963/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19809,7 +19809,7 @@
           <t>D | 436呎 (2房)
 $988万
 $22,656/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -19817,7 +19817,7 @@
           <t>E | 391呎 (2房)
 $874万
 $22,347/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -19833,7 +19833,7 @@
           <t>G | 340呎 (2房)
 $763万
 $22,456/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -19841,7 +19841,7 @@
           <t>H | 339呎 (2房)
 $802万
 $23,660/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -19849,7 +19849,7 @@
           <t>J | 339呎 (2房)
 $802万
 $23,652/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -19857,7 +19857,7 @@
           <t>K | 339呎 (2房)
 $793万
 $23,394/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -19865,7 +19865,7 @@
           <t>L | 338呎 (2房)
 $746万
 $22,058/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -19873,7 +19873,7 @@
           <t>M | 616呎 (3房)
 $1394万
 $22,638/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
           <t>A | 708呎 (3房)
 $1688万
 $23,848/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19896,7 +19896,7 @@
           <t>B | 610呎 (3房)
 $1471万
 $24,109/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -19912,7 +19912,7 @@
           <t>D | 436呎 (2房)
 $980万
 $22,487/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -19920,7 +19920,7 @@
           <t>E | 391呎 (2房)
 $869万
 $22,231/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19928,7 +19928,7 @@
           <t>F | 436呎 (2房)
 $1006万
 $23,067/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -19936,7 +19936,7 @@
           <t>G | 340呎 (2房)
 $759万
 $22,338/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,493/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,264/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>K | 339呎 (2房)
 $748万
 $22,063/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>L | 338呎 (2房)
 $758万
 $22,425/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>M | 616呎 (3房)
 $1413万
 $22,936/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
           <t>A | 708呎 (3房)
 $1673万
 $23,631/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19999,7 +19999,7 @@
           <t>B | 610呎 (3房)
 $1386万
 $22,722/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20007,7 +20007,7 @@
           <t>C | 431呎 (2房)
 $1035万
 $24,004/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20015,7 +20015,7 @@
           <t>D | 436呎 (2房)
 $973万
 $22,324/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -20023,7 +20023,7 @@
           <t>E | 391呎 (2房)
 $863万
 $22,080/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>F | 436呎 (2房)
 $998万
 $22,881/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>G | 340呎 (2房)
 $772万
 $22,692/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>H | 339呎 (2房)
 $751万
 $22,159/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,365/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>K | 339呎 (2房)
 $760万
 $22,432/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>L | 338呎 (2房)
 $738万
 $21,835/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>M | 616呎 (3房)
 $1372万
 $22,273/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
           <t>A | 708呎 (3房)
 $1577万
 $22,281/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>B | 610呎 (3房)
 $1379万
 $22,602/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>C | 431呎 (2房)
 $976万
 $22,653/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>D | 436呎 (2房)
 $987万
 $22,629/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>E | 391呎 (2房)
 $855万
 $21,875/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>F | 436呎 (2房)
 $987万
 $22,633/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>G | 340呎 (2房)
 $751万
 $22,078/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>H | 339呎 (2房)
 $746万
 $22,009/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>J | 339呎 (2房)
 $746万
 $22,012/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>K | 339呎 (2房)
 $758万
 $22,350/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,746/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>M | 616呎 (3房)
 $1387万
 $22,518/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -20197,7 +20197,7 @@
           <t>A | 708呎 (3房)
 $1569万
 $22,166/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,015/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>C | 431呎 (2房)
 $970万
 $22,497/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>D | 436呎 (2房)
 $960万
 $22,013/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>E | 391呎 (2房)
 $895万
 $22,897/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>F | 436呎 (2房)
 $1000万
 $22,947/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>G | 340呎 (2房)
 $745万
 $21,912/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -20253,7 +20253,7 @@
           <t>H | 339呎 (2房)
 $741万
 $21,867/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -20261,7 +20261,7 @@
           <t>J | 339呎 (2房)
 $744万
 $21,945/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -20269,7 +20269,7 @@
           <t>K | 339呎 (2房)
 $737万
 $21,730/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -20277,7 +20277,7 @@
           <t>L | 338呎 (2房)
 $730万
 $21,611/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -20285,7 +20285,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $22,998/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20300,7 @@
           <t>A | 708呎 (3房)
 $1561万
 $22,049/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>B | 610呎 (3房)
 $1367万
 $22,404/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>C | 431呎 (2房)
 $965万
 $22,381/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>D | 436呎 (2房)
 $955万
 $21,898/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -20332,7 +20332,7 @@
           <t>E | 391呎 (2房)
 $842万
 $21,533/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -20340,7 +20340,7 @@
           <t>F | 436呎 (2房)
 $971万
 $22,280/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -20348,7 +20348,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,295/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -20356,7 +20356,7 @@
           <t>H | 339呎 (2房)
 $738万
 $21,783/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>J | 339呎 (2房)
 $782万
 $23,063/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>K | 339呎 (2房)
 $750万
 $22,128/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>L | 338呎 (2房)
 $744万
 $22,004/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>M | 616呎 (3房)
 $1407万
 $22,836/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
           <t>A | 708呎 (3房)
 $1553万
 $21,935/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20411,7 +20411,7 @@
           <t>B | 610呎 (3房)
 $1361万
 $22,305/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20419,7 +20419,7 @@
           <t>C | 431呎 (2房)
 $979万
 $22,719/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20427,7 +20427,7 @@
           <t>D | 436呎 (2房)
 $952万
 $21,829/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -20435,7 +20435,7 @@
           <t>E | 391呎 (2房)
 $835万
 $21,365/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -20443,7 +20443,7 @@
           <t>F | 436呎 (2房)
 $1017万
 $23,322/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -20451,7 +20451,7 @@
           <t>G | 340呎 (2房)
 $738万
 $21,719/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -20459,7 +20459,7 @@
           <t>H | 339呎 (2房)
 $736万
 $21,703/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -20467,7 +20467,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,262/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -20475,7 +20475,7 @@
           <t>K | 339呎 (2房)
 $731万
 $21,577/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -20483,7 +20483,7 @@
           <t>L | 338呎 (2房)
 $725万
 $21,455/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -20491,7 +20491,7 @@
           <t>M | 616呎 (3房)
 $1324万
 $21,497/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20506,7 @@
           <t>A | 708呎 (3房)
 $1580万
 $22,323/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 610呎 (3房)
 $1355万
 $22,210/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 431呎 (2房)
 $972万
 $22,549/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20530,7 +20530,7 @@
           <t>D | 436呎 (2房)
 $969万
 $22,235/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 391呎 (2房)
 $876万
 $22,397/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -20546,7 +20546,7 @@
           <t>F | 436呎 (2房)
 $978万
 $22,427/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -20554,7 +20554,7 @@
           <t>G | 340呎 (2房)
 $735万
 $21,623/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -20562,7 +20562,7 @@
           <t>H | 339呎 (2房)
 $750万
 $22,117/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -20570,7 +20570,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -20578,7 +20578,7 @@
           <t>K | 339呎 (2房)
 $728万
 $21,480/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -20586,7 +20586,7 @@
           <t>L | 338呎 (2房)
 $722万
 $21,358/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>M | 616呎 (3房)
 $1315万
 $21,348/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
           <t>A | 708呎 (3房)
 $1539万
 $21,731/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20617,7 +20617,7 @@
           <t>B | 610呎 (3房)
 $1349万
 $22,117/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20625,7 +20625,7 @@
           <t>C | 431呎 (2房)
 $945万
 $21,931/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>D | 436呎 (2房)
 $944万
 $21,662/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>E | 391呎 (2房)
 $871万
 $22,279/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>F | 436呎 (2房)
 $948万
 $21,742/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -20657,7 +20657,7 @@
           <t>G | 340呎 (2房)
 $731万
 $21,505/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -20665,7 +20665,7 @@
           <t>H | 339呎 (2房)
 $732万
 $21,601/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -20673,7 +20673,7 @@
           <t>J | 339呎 (2房)
 $772万
 $22,771/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -20681,7 +20681,7 @@
           <t>K | 339呎 (2房)
 $725万
 $21,383/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -20689,7 +20689,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,731/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -20697,7 +20697,7 @@
           <t>M | 616呎 (3房)
 $1307万
 $21,215/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
           <t>A | 708呎 (3房)
 $1618万
 $22,846/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -20728,7 +20728,7 @@
           <t>C | 431呎 (2房)
 $940万
 $21,802/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -20736,7 +20736,7 @@
           <t>D | 436呎 (2房)
 $990万
 $22,716/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -20744,7 +20744,7 @@
           <t>E | 391呎 (2房)
 $822万
 $21,028/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -20752,7 +20752,7 @@
           <t>F | 436呎 (2房)
 $938万
 $21,516/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -20760,7 +20760,7 @@
           <t>G | 340呎 (2房)
 $743万
 $21,860/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -20768,7 +20768,7 @@
           <t>H | 339呎 (2房)
 $768万
 $22,643/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -20776,7 +20776,7 @@
           <t>J | 339呎 (2房)
 $767万
 $22,632/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -20784,7 +20784,7 @@
           <t>K | 339呎 (2房)
 $736万
 $21,722/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -20792,7 +20792,7 @@
           <t>L | 338呎 (2房)
 $731万
 $21,632/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -20800,7 +20800,7 @@
           <t>M | 616呎 (3房)
 $1328万
 $21,567/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20815,7 +20815,7 @@
           <t>A | 708呎 (3房)
 $1528万
 $21,575/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -20831,7 +20831,7 @@
           <t>C | 431呎 (2房)
 $934万
 $21,665/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -20839,7 +20839,7 @@
           <t>D | 436呎 (2房)
 $933万
 $21,400/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -20847,7 +20847,7 @@
           <t>E | 391呎 (2房)
 $819万
 $20,944/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -20855,7 +20855,7 @@
           <t>F | 436呎 (2房)
 $931万
 $21,343/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -20863,7 +20863,7 @@
           <t>G | 340呎 (2房)
 $724万
 $21,291/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -20871,7 +20871,7 @@
           <t>H | 339呎 (2房)
 $764万
 $22,544/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -20879,7 +20879,7 @@
           <t>J | 339呎 (2房)
 $764万
 $22,524/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -20887,7 +20887,7 @@
           <t>K | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -20895,7 +20895,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,208/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -20903,7 +20903,7 @@
           <t>M | 616呎 (3房)
 $1293万
 $20,989/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20918,7 @@
           <t>A | 708呎 (3房)
 $1604万
 $22,649/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -20926,7 +20926,7 @@
           <t>B | 610呎 (3房)
 $1399万
 $22,938/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -20934,7 +20934,7 @@
           <t>C | 431呎 (2房)
 $928万
 $21,542/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -20942,7 +20942,7 @@
           <t>D | 436呎 (2房)
 $928万
 $21,295/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -20950,7 +20950,7 @@
           <t>E | 391呎 (2房)
 $815万
 $20,837/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -20958,7 +20958,7 @@
           <t>F | 436呎 (2房)
 $923万
 $21,176/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -20966,7 +20966,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,300/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -20974,7 +20974,7 @@
           <t>H | 339呎 (2房)
 $720万
 $21,233/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -20982,7 +20982,7 @@
           <t>J | 339呎 (2房)
 $758万
 $22,363/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -20990,7 +20990,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,013/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -20998,7 +20998,7 @@
           <t>L | 338呎 (2房)
 $723万
 $21,404/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -21006,7 +21006,7 @@
           <t>M | 616呎 (3房)
 $1284万
 $20,841/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21021,7 @@
           <t>A | 708呎 (3房)
 $1548万
 $21,865/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21029,7 +21029,7 @@
           <t>B | 610呎 (3房)
 $1347万
 $22,087/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -21037,7 +21037,7 @@
           <t>C | 431呎 (2房)
 $923万
 $21,411/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -21045,7 +21045,7 @@
           <t>D | 436呎 (2房)
 $922万
 $21,147/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -21053,7 +21053,7 @@
           <t>E | 391呎 (2房)
 $808万
 $20,672/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -21061,7 +21061,7 @@
           <t>F | 436呎 (2房)
 $916万
 $21,007/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -21069,7 +21069,7 @@
           <t>G | 340呎 (2房)
 $752万
 $22,125/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -21077,7 +21077,7 @@
           <t>H | 339呎 (2房)
 $713万
 $21,045/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -21085,7 +21085,7 @@
           <t>J | 339呎 (2房)
 $752万
 $22,182/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -21093,7 +21093,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,046/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -21101,7 +21101,7 @@
           <t>L | 338呎 (2房)
 $703万
 $20,812/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -21109,7 +21109,7 @@
           <t>M | 616呎 (3房)
 $1275万
 $20,695/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21124,7 @@
           <t>A | 708呎 (3房)
 $1541万
 $21,771/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21132,7 +21132,7 @@
           <t>B | 610呎 (3房)
 $1309万
 $21,464/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -21140,7 +21140,7 @@
           <t>C | 431呎 (2房)
 $917万
 $21,283/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21148,7 +21148,7 @@
           <t>D | 436呎 (2房)
 $917万
 $21,022/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -21156,7 +21156,7 @@
           <t>E | 391呎 (2房)
 $802万
 $20,504/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -21164,7 +21164,7 @@
           <t>F | 436呎 (2房)
 $958万
 $21,983/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -21172,7 +21172,7 @@
           <t>G | 340呎 (2房)
 $707万
 $20,804/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -21180,7 +21180,7 @@
           <t>H | 339呎 (2房)
 $708万
 $20,892/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -21188,7 +21188,7 @@
           <t>J | 339呎 (2房)
 $708万
 $20,876/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -21196,7 +21196,7 @@
           <t>K | 339呎 (2房)
 $718万
 $21,190/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -21204,7 +21204,7 @@
           <t>L | 338呎 (2房)
 $699万
 $20,666/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -21212,7 +21212,7 @@
           <t>M | 616呎 (3房)
 $1267万
 $20,564/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
           <t>E | 391呎 (2房)
 $796万
 $20,357/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -21275,7 +21275,7 @@
           <t>G | 302呎 (2房)
 $727万
 $24,085/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -21283,7 +21283,7 @@
           <t>H | 301呎 (2房)
 $724万
 $24,056/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -21291,7 +21291,7 @@
           <t>J | 301呎 (2房)
 $723万
 $24,032/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -21299,7 +21299,7 @@
           <t>K | 301呎 (2房)
 $757万
 $25,142/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -21307,7 +21307,7 @@
           <t>L | 301呎 (2房)
 $714万
 $23,705/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -21315,7 +21315,7 @@
           <t>M | 616呎 (3房)
 $1256万
 $20,383/呎
-(26年-05月)</t>
+(26年-05月-09日)</t>
         </is>
       </c>
     </row>
